--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2018_aysen_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2018_aysen_provincial.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-04 13:57</t>
+    <t xml:space="preserve">2026-08-07 06:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2018_aysen_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2018_aysen_provincial.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-07 06:23</t>
+    <t xml:space="preserve">2026-08-13 12:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2018_aysen_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2018_aysen_provincial.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-13 12:43</t>
+    <t xml:space="preserve">2026-08-19 11:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2018_aysen_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2018_aysen_provincial.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 11:43</t>
+    <t xml:space="preserve">2026-08-28 10:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2018_aysen_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2018_aysen_provincial.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 10:52</t>
+    <t xml:space="preserve">2026-09-01 11:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2018_aysen_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2018_aysen_provincial.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-01 11:22</t>
+    <t xml:space="preserve">2026-09-04 19:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2018_aysen_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2018_aysen_provincial.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-04 19:59</t>
+    <t xml:space="preserve">2026-09-06 16:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2018_aysen_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2018_aysen_provincial.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 16:31</t>
+    <t xml:space="preserve">2026-09-08 11:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
